--- a/java/bundles/org.eclipse.set.feature/rootdir/data/export/excel/sszs_vorlage.xlsx
+++ b/java/bundles/org.eclipse.set.feature/rootdir/data/export/excel/sszs_vorlage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_intern\planpro\set\java\bundles\org.eclipse.set.feature\rootdir\data\export\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035A18A8-4321-4356-864E-68125CD84E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746BFB5F-B53B-42D6-8F6F-5E2407032E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sszs_Beispielbefüllung" sheetId="9" r:id="rId1"/>
@@ -705,15 +705,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -723,19 +735,7 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1183,198 +1183,198 @@
     </row>
     <row r="2" spans="1:35" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="42" t="s">
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="42" t="s">
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="42" t="s">
+      <c r="Q2" s="39"/>
+      <c r="R2" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="43"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="42" t="s">
+      <c r="S2" s="38"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="42" t="s">
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="39"/>
+      <c r="AC2" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="AD2" s="43"/>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="42" t="s">
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="39"/>
+      <c r="AF2" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="44"/>
-      <c r="AI2" s="45" t="s">
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="39"/>
+      <c r="AI2" s="36" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="37" t="s">
+      <c r="E3" s="42"/>
+      <c r="F3" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="I3" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="35" t="s">
+      <c r="K3" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="35" t="s">
+      <c r="L3" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="M3" s="35" t="s">
+      <c r="M3" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="35" t="s">
+      <c r="N3" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="38" t="s">
+      <c r="O3" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="P3" s="37" t="s">
+      <c r="P3" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="38" t="s">
+      <c r="Q3" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="R3" s="37" t="s">
+      <c r="R3" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="35" t="s">
+      <c r="S3" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="T3" s="38" t="s">
+      <c r="T3" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="U3" s="37" t="s">
+      <c r="U3" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="V3" s="35" t="s">
+      <c r="V3" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="W3" s="35" t="s">
+      <c r="W3" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="X3" s="35" t="s">
+      <c r="X3" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="Y3" s="35" t="s">
+      <c r="Y3" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="Z3" s="35" t="s">
+      <c r="Z3" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="AA3" s="35" t="s">
+      <c r="AA3" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AB3" s="38" t="s">
+      <c r="AB3" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="AC3" s="37" t="s">
+      <c r="AC3" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="AD3" s="35" t="s">
+      <c r="AD3" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="AE3" s="38" t="s">
+      <c r="AE3" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AF3" s="37" t="s">
+      <c r="AF3" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="AG3" s="35" t="s">
+      <c r="AG3" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="AH3" s="38" t="s">
+      <c r="AH3" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="AI3" s="36"/>
+      <c r="AI3" s="45"/>
     </row>
     <row r="4" spans="1:35" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="35"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="41"/>
       <c r="D4" s="27" t="s">
         <v>49</v>
       </c>
       <c r="E4" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="37"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="39"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="37"/>
-      <c r="AD4" s="35"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="37"/>
-      <c r="AG4" s="35"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="36"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="42"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="41"/>
+      <c r="AE4" s="42"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="42"/>
+      <c r="AI4" s="45"/>
     </row>
     <row r="5" spans="1:35" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
@@ -1384,7 +1384,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="41"/>
+      <c r="H5" s="35"/>
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
@@ -1449,14 +1449,14 @@
       <c r="S6" s="33"/>
       <c r="T6" s="33"/>
       <c r="U6" s="22"/>
-      <c r="V6" s="22"/>
+      <c r="V6" s="33"/>
       <c r="W6" s="33"/>
       <c r="X6" s="22"/>
       <c r="Y6" s="22"/>
       <c r="Z6" s="33"/>
-      <c r="AA6" s="21"/>
-      <c r="AB6" s="21"/>
-      <c r="AC6" s="21"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
       <c r="AD6" s="33"/>
       <c r="AE6" s="21"/>
       <c r="AF6" s="30"/>
@@ -1486,14 +1486,14 @@
       <c r="S7" s="33"/>
       <c r="T7" s="33"/>
       <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
+      <c r="V7" s="33"/>
       <c r="W7" s="33"/>
       <c r="X7" s="22"/>
       <c r="Y7" s="22"/>
       <c r="Z7" s="33"/>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
-      <c r="AC7" s="21"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
       <c r="AD7" s="33"/>
       <c r="AE7" s="21"/>
       <c r="AF7" s="30"/>
@@ -1781,6 +1781,30 @@
     <row r="62" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="AH3:AH4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="T3:T4"/>
     <mergeCell ref="AC2:AE2"/>
     <mergeCell ref="AF2:AH2"/>
     <mergeCell ref="B3:B4"/>
@@ -1797,30 +1821,6 @@
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="AH3:AH4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="AF3:AF4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.19685039370078741" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -1829,6 +1829,52 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100E758A0F93049BE4CAD441F10C0D8186D" ma:contentTypeVersion="5" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="fb340e34ecc5d059b634082484788e96">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="576ce185-3b2e-4f75-8b7c-efeb82226bea" xmlns:ns3="http://schemas.microsoft.com/sharepoint/v3/fields" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ae5cd419a40dc0c21009e0c04d2bd83e" ns2:_="" ns3:_="">
     <xsd:import namespace="576ce185-3b2e-4f75-8b7c-efeb82226bea"/>
@@ -2020,57 +2066,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2079,7 +2075,19 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FA61470-DD61-4999-8627-225AC049B66F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD45C59E-C13E-4B92-9551-AE1790848EFA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2098,26 +2106,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FA61470-DD61-4999-8627-225AC049B66F}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1C5838C-81AB-4B9A-B282-4E4B57DAFB8B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{947F1741-2986-4B63-8B5C-D0468C671233}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1C5838C-81AB-4B9A-B282-4E4B57DAFB8B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>